--- a/docs/Bilag-03_Tjekliste.xlsx
+++ b/docs/Bilag-03_Tjekliste.xlsx
@@ -799,9 +799,9 @@
       <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Alle henvisninger i kolonnen 'Henvisning til dokumentation/bilag' angiver et navngivet, nummereret bilag og et konkret afsnit, f.eks. 'Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.4'. Erhvervsstyrelsen accepterer ikke links eller kildefilstier som dokumentation.
-Bilag 1–3 og 4–13 udgør den skriftlige dokumentation (Bilag 1–2 og 4–13 som markdown i docs-mappen, konverteres til PDF ved indsendelse; Bilag 3 som xlsx). Bilag 14 er underskrevne underbehandler-DPA'er, der vedhæftes som separate PDF-filer ved indsendelsen via virk.dk. Se Bilag 2 (Bilag-02_Bilagsoversigt.md) for den komplette bilagsliste.
+Bilag 1–16 (undtagen Bilag 14) udgør den skriftlige dokumentation (Bilag 1–2, 4–13 og 15–16 som markdown i docs-mappen, konverteres til PDF ved indsendelse; Bilag 3 som xlsx). Bilag 14 er underskrevne underbehandler-DPA'er, der vedhæftes som separate PDF-filer ved indsendelsen via virk.dk. Se Bilag 2 (Bilag-02_Bilagsoversigt.md) for den komplette bilagsliste.
 Kildefilstier (src/..., prisma/...) er angivet særskilt i kolonnen 'Teknisk kilde (supplerende, ikke dokumentation)' som supplerende information og udgør ikke dokumentationshenvisningen.
-Status 'Delvist' gælder: kreditnota-afsendelse (send-pipeline hardcoder type 380), bank-integration (kun Tink + Demo reelle; Nordea/Danske/Jyske er stubs) og uforanderlighed (audit-log uforanderlig; ingen kryptografisk hash-chain på posteringer). Se Bilag 12 (Bilag-12_Udbedringsplan.md).</t>
+Status 'Delvist' gælder: bank-integration (kun Tink + Demo reelle; Nordea/Danske/Jyske er stubs) og uforanderlighed (audit-log uforanderlig; ingen kryptografisk hash-chain på posteringer). Kreditnota-afsendelse (OIOUBL/Peppol BIS type 381) er nu fuldt understøttet. Se Bilag 12 (Bilag-12_Udbedringsplan.md).</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>Version: 2.0 — 2026 (revideret med præcise dokumentationshenvisninger efter Erhvervsstyrelsens svar i sagen)</t>
+          <t>Version: 2.1 — September 2026 (Sproom har erstattet Storecove som Peppol/NemHandel Access Point; kreditnota type 381 nu fuldt understøttet i send-pipeline; Tink er reel integration; krydsreferencer ajourført)</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E2" s="30" t="inlineStr">
         <is>
-          <t>OIOUBL 2.1 (type 380) via Storecove/NemHandel.</t>
+          <t>OIOUBL 2.1 (type 380) via Sproom/NemHandel — raw XML POST /api/documents.</t>
         </is>
       </c>
       <c r="F2" s="30" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="G2" s="30" t="inlineStr">
         <is>
-          <t>src/lib/oioubl-generator.ts; src/app/api/invoices/[id]/oioubl/route.ts; src/lib/einvoice-sender.ts; src/lib/nemhandel-client.ts</t>
+          <t>src/lib/oioubl-generator.ts; src/app/api/invoices/[id]/oioubl/route.ts; src/lib/einvoice-sender.ts; src/lib/sproom-client.ts</t>
         </is>
       </c>
     </row>
@@ -3066,22 +3066,22 @@
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>Delvist</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Kreditnota-oprettelsesflow er implementeret i UI (KRE-{år}-{seq}, spejlet bogføring), og OIOUBL-download-endpoint returnerer korrekt type 381. MEN einvoice-sender.ts hardcoder invoiceTypeCode='380' i buildOIOUBLData(), og queueEInvoiceSend henter ikke invoice.documentType — kreditnota sendes derfor som type 380 (almindelig faktura) i stedet for 381. Kreditnota kan ikke reelt afsendes som OIOUBL type 381.</t>
+          <t>Kreditnotaer afsendes som OIOUBL type 381: einvoice-sender.ts vælger invoiceTypeCode ud fra invoice.documentType === 'CREDIT_NOTE' (fallback creditNotePrefix 'KRE-'), og oioubl-generator.ts emitterer korrekt &lt;CreditNote&gt;-rodelement med cac:CreditNoteLine/cbc:CreditedQuantity og cac:BillingReference til originalfakturaen. Fuldt understøttet.</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 + Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 6 + Bilag 12 (Bilag-12_Udbedringsplan.md). Delvist: oprettelsesflow og download (381) virker, men send-pipeline hardcoder type 380.</t>
+          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 + Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 6.4. Fuldt understøttet: kreditnotaer sendes som type 381 (CreditNote-rod + BillingReference).</t>
         </is>
       </c>
       <c r="G4" s="30" t="inlineStr">
         <is>
-          <t>src/lib/oioubl-generator.ts (type 381); src/app/api/invoices/[id]/oioubl/route.ts; src/lib/einvoice-sender.ts (hardcoder 380)</t>
+          <t>src/lib/oioubl-generator.ts (&lt;CreditNote&gt;-rod, type 381); src/app/api/invoices/[id]/oioubl/route.ts; src/lib/einvoice-sender.ts (vælger 381/380 ud fra documentType)</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="E7" s="30" t="inlineStr">
         <is>
-          <t>Peppol BIS Billing 3.0 via Storecove Access Point.</t>
+          <t>Peppol BIS Billing 3.0 via Sproom Access Point (dansk AP — Peppol + NemHandel).</t>
         </is>
       </c>
       <c r="F7" s="30" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="G7" s="30" t="inlineStr">
         <is>
-          <t>src/lib/einvoice-sender.ts; src/lib/nemhandel-client.ts; src/components/invoices/send-einvoice-dialog.tsx</t>
+          <t>src/lib/einvoice-sender.ts; src/lib/sproom-client.ts; src/components/invoices/send-einvoice-dialog.tsx</t>
         </is>
       </c>
     </row>
@@ -3251,22 +3251,22 @@
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
-          <t>Delvist</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E9" s="30" t="inlineStr">
         <is>
-          <t>Samme begrænsning som OIOUBL kreditnota — oprettelsesflow er implementeret, men send-pipeline (einvoice-sender.ts) hardcoder type 380. Peppol BIS-afsendelse transmitterer derfor 380 i stedet for 381. Kreditnota kan ikke reelt afsendes som Peppol BIS kreditnota.</t>
+          <t>Kreditnotaer afsendes som Peppol BIS Billing 3.0 type 381 via Sproom — samme pipeline som OIOUBL (documentType CREDIT_NOTE vælger 381 med BillingReference). Fuldt understøttet.</t>
         </is>
       </c>
       <c r="F9" s="30" t="inlineStr">
         <is>
-          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 + Bilag 12 (Bilag-12_Udbedringsplan.md). Delvist.</t>
+          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 + Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 6.4. Fuldt understøttet.</t>
         </is>
       </c>
       <c r="G9" s="30" t="inlineStr">
         <is>
-          <t>src/lib/oioubl-generator.ts; src/lib/einvoice-sender.ts</t>
+          <t>src/lib/oioubl-generator.ts; src/lib/einvoice-sender.ts; src/lib/sproom-client.ts</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (bank) + Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (bankforbindelser) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 12 + Bilag 12 (Bilag-12_Udbedringsplan.md). Delvist: kun Tink + Demo reelle.</t>
+          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (bank) + Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (bankforbindelser) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 7 + Bilag 12 (Bilag-12_Udbedringsplan.md). Delvist: kun Tink + Demo reelle.</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F15" s="30" t="inlineStr">
         <is>
-          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (PSD2 consent-flow) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 12. Delvist: consent virker for Tink; stubs for øvrige banker.</t>
+          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (PSD2 consent-flow) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 7. Delvist: consent virker for Tink; stubs for øvrige banker.</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr">
@@ -4070,17 +4070,17 @@
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
-          <t>Tilmelding via Storecove (Peppol/NemHandel Access Point).</t>
+          <t>Tilmelding via Sproom (Peppol/NemHandel Access Point) — child company pr. CVR oprettes automatisk og registreres i begge netværk.</t>
         </is>
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 16.3 + Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (Storecove som Access Point) + Bilag 12 (Bilag-12_Udbedringsplan.md) afsnit 6 (mangel 5 — NemHandel simulering ved manglende AP-aftale).</t>
+          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 16.3 + Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (Sproom som Access Point) + Bilag 12 (Bilag-12_Udbedringsplan.md) U-9 (Sproom-aftale indgået — staging aktiv, produktion via env-switch).</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
-          <t>src/app/api/company/einvoice-register/route.ts; src/lib/einvoice-sender.ts; src/lib/nemhandel-client.ts; src/lib/storecove-client.ts</t>
+          <t>src/app/api/company/einvoice-register/route.ts; src/app/api/sproom/create-child-company/route.ts; src/app/api/sproom/register-nemhandel/route.ts; src/lib/sproom-client.ts</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="34" t="inlineStr">
         <is>
-          <t>Statusoversigt — AlphaFlow Tjekliste (Version 2.0 — 2026)</t>
+          <t>Statusoversigt — AlphaFlow Tjekliste (Version 2.1 — September 2026)</t>
         </is>
       </c>
     </row>
@@ -4280,38 +4280,26 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="39" t="inlineStr">
         <is>
-          <t>• Hovedkrav nr. 3 — 'Sende kreditnota i OIOUBL' (Bilag 4, 1, c): Oprettelsesflow er implementeret, men send-pipeline (einvoice-sender.ts) hardcoder type 380. Jf. Bilag 12 (Bilag-12_Udbedringsplan.md).</t>
+          <t>• Hovedkrav nr. 3 — 'Automatisk bankintegration' (Bilag 4, 3, b): Tink + Demo er reelle; Nordea/Danske Bank/Jyske Bank er stubs. Jf. Bilag 1 afsnit 8 punkt 7.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="39" t="inlineStr">
         <is>
-          <t>• Hovedkrav nr. 3 — 'Sende kreditnota i Peppol BIS' (Bilag 4, 2, c): Samme begrænsning som OIOUBL kreditnota — oprettelsesflow implementeret, men send-pipeline hardcoder type 380.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>• Hovedkrav nr. 3 — 'Automatisk bankintegration' (Bilag 4, 3, b): Tink + Demo er reelle; Nordea/Danske Bank/Jyske Bank er stubs. Jf. Bilag 1 afsnit 8 punkt 12.</t>
-        </is>
-      </c>
-    </row>
+          <t>• Hovedkrav nr. 3 — 'PSD2 bankhåndtering' (Bilag 4, 3, c): Consent-flow virker for Tink; sandbox-stubs for øvrige banker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1"/>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="39" t="inlineStr">
-        <is>
-          <t>• Hovedkrav nr. 3 — 'PSD2 bankhåndtering' (Bilag 4, 3, c): Consent-flow virker for Tink; sandbox-stubs for øvrige banker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Komplet bilagsliste: se Bilag 2 (Bilag-02_Bilagsoversigt.md). Lovgrundlag: Lov om bogføring (LOV nr. 700 af 24. maj 2022); BEK nr. 97 af 26. januar 2023; BEK nr. 98 af 26. januar 2023.</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A16:F16"/>

--- a/docs/Bilag-03_Tjekliste.xlsx
+++ b/docs/Bilag-03_Tjekliste.xlsx
@@ -270,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -845,9 +848,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>Version: 2.1 — September 2026 (Sproom har erstattet Storecove som Peppol/NemHandel Access Point; kreditnota type 381 nu fuldt understøttet i send-pipeline; Tink er reel integration; krydsreferencer ajourført)</t>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Version: 2.2 — Oktober 2026 (Storecove-kode fuldt fjernet fra kodebasen — Sproom er eneste Access Point; DB-felter og enum-værdier omdøbt: storecoveSubmissionId→sproomDocumentId, STORECOVE→SPROOM_AUTO; legacy PUBLIC_STANDARD_CHART fjernet — kun OFFICIAL_STANDARD_CHART 603 konti benyttes; krydsreferencer ajourført)</t>
         </is>
       </c>
     </row>
